--- a/packages/office-reader/src/spreadsheet/fixtures/date1904.xlsx
+++ b/packages/office-reader/src/spreadsheet/fixtures/date1904.xlsx
@@ -1,9 +1,10 @@
 
 <file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="https://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0"/>
     <xf numFmtId="14"/>
+    <xf numFmtId="20"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -24,6 +25,9 @@
       <x:c r="A1" s="1">
         <x:v>44712</x:v>
       </x:c>
+      <x:c r="B1" s="2">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
 </x:worksheet>
